--- a/InputData/trans/BPP/Battery Pack Price.xlsx
+++ b/InputData/trans/BPP/Battery Pack Price.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BPP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\BPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C5ECB2E4-46DF-4367-A783-5F31E1460F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170D1734-2E5D-4D61-9071-C8405F09E6BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7076CB28-61DD-47F5-AE13-A59E054F1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,9 +146,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +186,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -292,7 +292,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -434,7 +434,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -443,18 +443,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.40625" customWidth="1"/>
+    <col min="2" max="2" width="101.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -462,32 +462,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -508,10 +508,10 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -605,8 +605,68 @@
       <c r="AE1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -701,6 +761,66 @@
         <v>0</v>
       </c>
       <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
         <v>0</v>
       </c>
     </row>
@@ -715,9 +835,9 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -725,7 +845,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -740,21 +860,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -898,14 +1003,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C3B3C5C-201F-4528-9C86-EBD693CAD12F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F0F99D9-296A-4796-81B6-0ADFBD815F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85930DE3-387E-4298-B73E-3C028184DC57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85930DE3-387E-4298-B73E-3C028184DC57}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F0F99D9-296A-4796-81B6-0ADFBD815F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C3B3C5C-201F-4528-9C86-EBD693CAD12F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/BPP/Battery Pack Price.xlsx
+++ b/InputData/trans/BPP/Battery Pack Price.xlsx
@@ -1,27 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\BPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7076CB28-61DD-47F5-AE13-A59E054F1AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96B753C-C214-454C-A5B3-CF084553B72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BPP" sheetId="2" r:id="rId2"/>
     <sheet name="SYBPP" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,36 +35,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>BNEF</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>$/kWh</t>
+  </si>
   <si>
     <t>BPP Battery Pack Price</t>
   </si>
   <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>BNEF</t>
-  </si>
-  <si>
-    <t>Lithium-ion Battery Pack Prices Hit Record Low of $139/kWh</t>
-  </si>
-  <si>
-    <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-hit-record-low-of-139-kwh/#:~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030.</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
     <t>The EPS applies endogenous learning for battery pack prices in years where the battery pack price is listed as 0.</t>
   </si>
   <si>
-    <t>2023 to 2012</t>
-  </si>
-  <si>
-    <t>$/kWh</t>
-  </si>
-  <si>
-    <t>Price</t>
+    <t>2025 to 2012</t>
+  </si>
+  <si>
+    <t>https://www.usinflationcalculator.com/</t>
+  </si>
+  <si>
+    <t>https://about.bnef.com/insights/clean-transport/lithium-ion-battery-pack-prices-fall-to-108-per-kilowatt-hour-despite-rising-metal-prices-bloombergnef/</t>
+  </si>
+  <si>
+    <t>Lithium-Ion Battery Pack Prices Fall to $108 Per Kilowatt-Hour, Despite Rising Metal Prices</t>
   </si>
 </sst>
 </file>
@@ -442,63 +442,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.40625" customWidth="1"/>
-    <col min="2" max="2" width="101.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="101.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>0.75350342301658668</v>
+        <v>0.71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" location=":~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030" xr:uid="{96C10B99-B75C-4A91-A1D1-2211BAD3764D}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -508,12 +508,12 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:BB2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -665,28 +665,39 @@
       <c r="AY1">
         <v>2070</v>
       </c>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.75">
+      <c r="AZ1">
+        <v>2071</v>
+      </c>
+      <c r="BA1">
+        <v>2072</v>
+      </c>
+      <c r="BB1">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>150*About!$B$11</f>
-        <v>113.025513452488</v>
+        <f t="shared" ref="B2:C2" si="0">C2</f>
+        <v>105.08</v>
       </c>
       <c r="C2">
-        <f>161*About!$B$11</f>
-        <v>121.31405110567046</v>
+        <f t="shared" si="0"/>
+        <v>105.08</v>
       </c>
       <c r="D2">
-        <f>139*About!$B$11</f>
-        <v>104.73697579930555</v>
+        <f>SYBPP!B2</f>
+        <v>105.08</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f>118*About!B11</f>
+        <v>83.78</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <f>108*About!B11</f>
+        <v>76.679999999999993</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -821,6 +832,15 @@
         <v>0</v>
       </c>
       <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
         <v>0</v>
       </c>
     </row>
@@ -835,220 +855,26 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>160*About!B11</f>
-        <v>120.56054768265386</v>
+        <f>148*About!B11</f>
+        <v>105.08</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F0F99D9-296A-4796-81B6-0ADFBD815F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85930DE3-387E-4298-B73E-3C028184DC57}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C3B3C5C-201F-4528-9C86-EBD693CAD12F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>